--- a/artfynd/A 27315-2025 artfynd.xlsx
+++ b/artfynd/A 27315-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116118699</v>
+        <v>137514510</v>
       </c>
       <c r="B2" t="n">
-        <v>96708</v>
+        <v>83512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,27 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>484177</v>
+        <v>484103</v>
       </c>
       <c r="R2" t="n">
-        <v>6323635</v>
+        <v>6323501</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,6 +766,16 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Tallbevuxen högmosse</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Vedyta på tallhögstubbe</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -781,51 +790,44 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116118699</t>
+          <t>https://artportalen.se/Sighting/137514510</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128806789</v>
+        <v>116118699</v>
       </c>
       <c r="B3" t="n">
-        <v>92841</v>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4745</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484103</v>
+        <v>484177</v>
       </c>
       <c r="R3" t="n">
-        <v>6323501</v>
+        <v>6323635</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,16 +883,6 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Mosse med tall</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Dikad högmosse med tall.</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -905,16 +897,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128806789</t>
+          <t>https://artportalen.se/Sighting/116118699</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132147102</v>
+        <v>128806789</v>
       </c>
       <c r="B4" t="n">
-        <v>57896</v>
+        <v>92841</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,21 +914,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100001</v>
+        <v>4745</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -944,17 +936,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -962,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484177</v>
+        <v>484103</v>
       </c>
       <c r="R4" t="n">
-        <v>6323635</v>
+        <v>6323501</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,22 +979,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,8 +993,19 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Mosse med tall</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Dikad högmosse med tall.</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1033,33 +1021,33 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132147102</t>
+          <t>https://artportalen.se/Sighting/128806789</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133352448</v>
+        <v>132147102</v>
       </c>
       <c r="B5" t="n">
-        <v>57972</v>
+        <v>57896</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1073,10 +1061,14 @@
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1086,13 +1078,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484103</v>
+        <v>484177</v>
       </c>
       <c r="R5" t="n">
-        <v>6323501</v>
+        <v>6323635</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1116,22 +1108,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,16 +1149,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133352448</t>
+          <t>https://artportalen.se/Sighting/132147102</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113688722</v>
+        <v>133352448</v>
       </c>
       <c r="B6" t="n">
-        <v>57141</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,29 +1166,33 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1206,13 +1202,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484177</v>
+        <v>484103</v>
       </c>
       <c r="R6" t="n">
-        <v>6323635</v>
+        <v>6323501</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1236,12 +1232,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1267,16 +1273,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113688722</t>
+          <t>https://artportalen.se/Sighting/133352448</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133352464</v>
+        <v>113688722</v>
       </c>
       <c r="B7" t="n">
-        <v>57162</v>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,13 +1322,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484103</v>
+        <v>484177</v>
       </c>
       <c r="R7" t="n">
-        <v>6323501</v>
+        <v>6323635</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1346,22 +1352,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,16 +1383,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133352464</t>
+          <t>https://artportalen.se/Sighting/113688722</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113689362</v>
+        <v>133352464</v>
       </c>
       <c r="B8" t="n">
-        <v>58327</v>
+        <v>57162</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1404,21 +1400,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1426,7 +1422,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1436,13 +1432,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484177</v>
+        <v>484103</v>
       </c>
       <c r="R8" t="n">
-        <v>6323635</v>
+        <v>6323501</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1466,22 +1462,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1507,50 +1503,46 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113689362</t>
+          <t>https://artportalen.se/Sighting/133352464</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111325650</v>
+        <v>113689362</v>
       </c>
       <c r="B9" t="n">
-        <v>58114</v>
+        <v>58327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1590,12 +1582,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-08-07</t>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-08-07</t>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1621,16 +1623,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111325650</t>
+          <t>https://artportalen.se/Sighting/113689362</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133352435</v>
+        <v>111325650</v>
       </c>
       <c r="B10" t="n">
-        <v>58136</v>
+        <v>58114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,14 +1659,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1674,13 +1676,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>484103</v>
+        <v>484177</v>
       </c>
       <c r="R10" t="n">
-        <v>6323501</v>
+        <v>6323635</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1704,22 +1706,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1744,6 +1736,130 @@
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111325650</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>133352435</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Basevad, mossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>484103</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6323501</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Per Fogelström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Per Fogelström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/133352435</t>
         </is>
@@ -1760,6 +1876,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27315-2025 artfynd.xlsx
+++ b/artfynd/A 27315-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137514510</v>
       </c>
       <c r="B2" t="n">
-        <v>83512</v>
+        <v>83515</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
